--- a/output/full_scan/batch_seq8_2026-06-29.xlsx
+++ b/output/full_scan/batch_seq8_2026-06-29.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -898,21 +898,21 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7714</v>
+        <v>7610</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>651.2381109800285</v>
+        <v>652.5510633994744</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>138</v>
+        <v>2100</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>60.17967338337145</v>
+        <v>60.99105078890215</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.92702316786866</v>
+        <v>49.53536179887997</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9921771023663905</v>
+        <v>0.4318682407749566</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.3895978073442585</v>
+        <v>-15.27404215737016</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7631</v>
+        <v>7714</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>637</v>
+        <v>651.2381109800285</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>65.79466218620077</v>
+        <v>60.17967338337145</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16.86566430945315</v>
+        <v>22.92702316786866</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7.576654272085612</v>
+        <v>0.9921771023663905</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>5.5794241293405</v>
+        <v>0.3895978073442585</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7799</v>
+        <v>7631</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>630.6668860230883</v>
+        <v>637</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>416.5</v>
+        <v>177</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>62.56344242646259</v>
+        <v>65.79466218620077</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>35.53698783630155</v>
+        <v>16.86566430945315</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.035213110194352</v>
+        <v>7.576654272085612</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>5.705567396583534</v>
+        <v>5.5794241293405</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8040</v>
+        <v>7799</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>625.2628175709236</v>
+        <v>630.6668860230883</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>102</v>
+        <v>416.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>50.67539698330949</v>
+        <v>62.56344242646259</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>35.11797974244413</v>
+        <v>35.53698783630155</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.7944169086546612</v>
+        <v>1.035213110194352</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0171399148699125</v>
+        <v>5.705567396583534</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8043</v>
+        <v>8040</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>614.8067233133814</v>
+        <v>625.2628175709236</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>176.5</v>
+        <v>102</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>51.3721018098265</v>
+        <v>50.67539698330949</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>36.89620675271017</v>
+        <v>35.11797974244413</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.3713113884538119</v>
+        <v>0.7944169086546612</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-5.015383696416102</v>
+        <v>0.0171399148699125</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1163,21 +1163,21 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8028</v>
+        <v>8043</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>597.258407372977</v>
+        <v>614.8067233133814</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>288.5</v>
+        <v>176.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>44.76165203929905</v>
+        <v>51.3721018098265</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>33.8486754484741</v>
+        <v>36.89620675271017</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.5978253894833262</v>
+        <v>0.3713113884538119</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-6.552122170454137</v>
+        <v>-5.015383696416102</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8024</v>
+        <v>8028</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>586.2515594468393</v>
+        <v>597.258407372977</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16.25</v>
+        <v>288.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>73.97811042937617</v>
+        <v>44.76165203929905</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>35.0090520155106</v>
+        <v>33.8486754484741</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.225155944683933</v>
+        <v>0.5978253894833262</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.5337343043696644</v>
+        <v>-6.552122170454137</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8044</v>
+        <v>8024</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>568.4348334334512</v>
+        <v>586.2515594468393</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>28.8</v>
+        <v>16.25</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>49.30250339326402</v>
+        <v>73.97811042937617</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20.83159633618254</v>
+        <v>35.0090520155106</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3548723036330088</v>
+        <v>2.225155944683933</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.3404423448167055</v>
+        <v>0.5337343043696644</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6916</v>
+        <v>8044</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>552.67024120331</v>
+        <v>568.4348334334512</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>20.05</v>
+        <v>28.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>49.92855704031681</v>
+        <v>49.30250339326402</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.63893942142775</v>
+        <v>20.83159633618254</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.3910535134031304</v>
+        <v>0.3548723036330088</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.1437623329466915</v>
+        <v>-0.3404423448167055</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8046</v>
+        <v>8021</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>552.4507453097863</v>
+        <v>559.2401007186847</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1080</v>
+        <v>522</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>65.53997944770057</v>
+        <v>53.57658533558794</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>18.54998235113335</v>
+        <v>22.43437319544386</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.179295468089513</v>
+        <v>0.2714496541185896</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>24.40496061244885</v>
+        <v>-3.133351862606929</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8032</v>
+        <v>6916</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>538.7828831898294</v>
+        <v>552.67024120331</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>42.9</v>
+        <v>20.05</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>44.10287705159313</v>
+        <v>49.92855704031681</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.76612022063561</v>
+        <v>28.63893942142775</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5357341396455709</v>
+        <v>0.3910535134031304</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.3999689262557026</v>
+        <v>-0.1437623329466915</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6890</v>
+        <v>8046</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>537.5250519365561</v>
+        <v>552.4507453097863</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>201.5</v>
+        <v>1080</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>43.39018132182125</v>
+        <v>65.53997944770057</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>26.32116757866742</v>
+        <v>18.54998235113335</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5762387369097748</v>
+        <v>1.179295468089513</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-5.849588110598271</v>
+        <v>24.40496061244885</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7827</v>
+        <v>8032</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>534.599958924063</v>
+        <v>538.7828831898294</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>171.5</v>
+        <v>42.9</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>63.08846968729728</v>
+        <v>44.10287705159313</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>21.35878200594722</v>
+        <v>23.76612022063561</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4138730838589488</v>
+        <v>0.5357341396455709</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.5124176525508846</v>
+        <v>-0.3999689262557026</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6870</v>
+        <v>6890</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>533.7524600666907</v>
+        <v>537.5250519365561</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>244.5</v>
+        <v>201.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>43.2365514134607</v>
+        <v>43.39018132182125</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23.5042715874729</v>
+        <v>26.32116757866742</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4527515929823795</v>
+        <v>0.5762387369097748</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-7.77456751142218</v>
+        <v>-5.849588110598271</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7715</v>
+        <v>7827</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>531.7493069948592</v>
+        <v>534.599958924063</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>34</v>
+        <v>171.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>60.87393917694651</v>
+        <v>63.08846968729728</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>42.35998593761238</v>
+        <v>21.35878200594722</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.721132498426524</v>
+        <v>0.4138730838589488</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.5672060158003607</v>
+        <v>0.5124176525508846</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6996</v>
+        <v>6870</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>517.6699991106557</v>
+        <v>533.7524600666907</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>195</v>
+        <v>244.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>52.45784005437344</v>
+        <v>43.2365514134607</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.14359119846027</v>
+        <v>23.5042715874729</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2143681459774629</v>
+        <v>0.4527515929823795</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.4417297515923724</v>
+        <v>-7.77456751142218</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6907</v>
+        <v>7715</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>516.6650585148708</v>
+        <v>531.7493069948592</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>140.5</v>
+        <v>34</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>51.16506240433389</v>
+        <v>60.87393917694651</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>29.0395346755681</v>
+        <v>42.35998593761238</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.2136301683571203</v>
+        <v>0.721132498426524</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.3350888471558457</v>
+        <v>0.5672060158003607</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6861</v>
+        <v>6996</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>509.2319611303541</v>
+        <v>517.6699991106557</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>319.5</v>
+        <v>195</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>44.05355148908436</v>
+        <v>52.45784005437344</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>21.55530611812986</v>
+        <v>23.14359119846027</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5193398616790532</v>
+        <v>0.2143681459774629</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-4.50075885045892</v>
+        <v>-0.4417297515923724</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6944</v>
+        <v>6907</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>507.9877473865822</v>
+        <v>516.6650585148708</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>984</v>
+        <v>140.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.36577002158671</v>
+        <v>51.16506240433389</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>17.44268614642263</v>
+        <v>29.0395346755681</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.584493264837598</v>
+        <v>0.2136301683571203</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-2.020079423171246</v>
+        <v>-0.3350888471558457</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7402</v>
+        <v>6861</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>502.2981992882451</v>
+        <v>509.2319611303541</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>109</v>
+        <v>319.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>63.05181725222942</v>
+        <v>44.05355148908436</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.35196777114676</v>
+        <v>21.55530611812986</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.220548697392092</v>
+        <v>0.5193398616790532</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>2.039678060344375</v>
+        <v>-4.50075885045892</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7749</v>
+        <v>6944</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>501.6830811622245</v>
+        <v>507.9877473865822</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>414</v>
+        <v>984</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>32.6794471294096</v>
+        <v>52.36577002158671</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>20.69194231619526</v>
+        <v>17.44268614642263</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4087534247575071</v>
+        <v>0.584493264837598</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-9.325891412514109</v>
+        <v>-2.020079423171246</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6901</v>
+        <v>7402</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>487.0527755005677</v>
+        <v>502.2981992882451</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>18.05</v>
+        <v>109</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>66.88119441042116</v>
+        <v>63.05181725222942</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>43.85618863887245</v>
+        <v>19.35196777114676</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.9959750898247036</v>
+        <v>2.220548697392092</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.2356918148434027</v>
+        <v>2.039678060344375</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6902</v>
+        <v>7749</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>473.9945672626786</v>
+        <v>501.6830811622245</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>126</v>
+        <v>414</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>44.92504061300322</v>
+        <v>32.6794471294096</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>25.14412276416186</v>
+        <v>20.69194231619526</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3466359719883543</v>
+        <v>0.4087534247575071</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-1.941979778273796</v>
+        <v>-9.325891412514109</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6914</v>
+        <v>6901</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>465.0081047500286</v>
+        <v>487.0527755005677</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>143</v>
+        <v>18.05</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.42945317139322</v>
+        <v>66.88119441042116</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11.35445214799965</v>
+        <v>43.85618863887245</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.114570382194241</v>
+        <v>0.9959750898247036</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.2628688768390563</v>
+        <v>0.2356918148434027</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7750</v>
+        <v>6902</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>449.876858712543</v>
+        <v>473.9945672626786</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>2065</v>
+        <v>126</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>42.47192007193502</v>
+        <v>44.92504061300322</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.39458274932723</v>
+        <v>25.14412276416186</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.6444385389294329</v>
+        <v>0.3466359719883543</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-22.2633023153734</v>
+        <v>-1.941979778273796</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6922</v>
+        <v>6914</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>445.17417300382</v>
+        <v>465.0081047500286</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>170.5</v>
+        <v>143</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>39.42402337533419</v>
+        <v>51.42945317139322</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>16.97292592447953</v>
+        <v>11.35445214799965</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.1993388178119887</v>
+        <v>1.114570382194241</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-2.71974382625342</v>
+        <v>0.2628688768390563</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6933</v>
+        <v>7750</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>441.9020858876164</v>
+        <v>449.876858712543</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>139</v>
+        <v>2065</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>35.21599880029711</v>
+        <v>42.47192007193502</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.29490555684221</v>
+        <v>20.39458274932723</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.2689780061411623</v>
+        <v>0.6444385389294329</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-1.883534564986487</v>
+        <v>-22.2633023153734</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2329,21 +2329,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7822</v>
+        <v>6922</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>437.2106132996342</v>
+        <v>445.17417300382</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1060</v>
+        <v>170.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>43.75450150966498</v>
+        <v>39.42402337533419</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>18.92465018581401</v>
+        <v>16.97292592447953</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5318217111557189</v>
+        <v>0.1993388178119887</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>10.76309522786195</v>
+        <v>-2.71974382625342</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7751</v>
+        <v>6933</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>430.6308725337914</v>
+        <v>441.9020858876164</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1330</v>
+        <v>139</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>36.42795978701601</v>
+        <v>35.21599880029711</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.91714603795053</v>
+        <v>21.29490555684221</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3429996559980802</v>
+        <v>0.2689780061411623</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>3.940611986088527</v>
+        <v>-1.883534564986487</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6903</v>
+        <v>7822</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>416.6714095973218</v>
+        <v>437.2106132996342</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>380</v>
+        <v>1060</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46.99405441756196</v>
+        <v>43.75450150966498</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>11.87290486220153</v>
+        <v>18.92465018581401</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7235645564130319</v>
+        <v>0.5318217111557189</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.653485368787535</v>
+        <v>10.76309522786195</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6906</v>
+        <v>7751</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>414.6677937686085</v>
+        <v>430.6308725337914</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>88.90000000000001</v>
+        <v>1330</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.6225358933438</v>
+        <v>36.42795978701601</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.45374942378191</v>
+        <v>13.91714603795053</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3904112646926598</v>
+        <v>0.3429996559980802</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-1.520557430811722</v>
+        <v>3.940611986088527</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6859</v>
+        <v>6903</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>404.5779151398206</v>
+        <v>416.6714095973218</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>122.5</v>
+        <v>380</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>43.89101719827289</v>
+        <v>46.99405441756196</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25.78453061211447</v>
+        <v>11.87290486220153</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.334979301578763</v>
+        <v>0.7235645564130319</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.05315445042939</v>
+        <v>-1.653485368787535</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7768</v>
+        <v>6906</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>378.7599873086991</v>
+        <v>414.6677937686085</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>333.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>32.81735285799225</v>
+        <v>49.6225358933438</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>21.19317263682149</v>
+        <v>22.45374942378191</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3016831167137448</v>
+        <v>0.3904112646926598</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-5.205879650430742</v>
+        <v>-1.520557430811722</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6877</v>
+        <v>6859</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>376.6250367080219</v>
+        <v>404.5779151398206</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>119</v>
+        <v>122.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>34.08284963564368</v>
+        <v>43.89101719827289</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>19.17828688107932</v>
+        <v>25.78453061211447</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.548146622240816</v>
+        <v>0.334979301578763</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.801403919206356</v>
+        <v>-1.05315445042939</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6887</v>
+        <v>7768</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>376.5707570320053</v>
+        <v>378.7599873086991</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>36.05</v>
+        <v>333.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.95140835957848</v>
+        <v>32.81735285799225</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>6.687171541263587</v>
+        <v>21.19317263682149</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7932768671587173</v>
+        <v>0.3016831167137448</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2452328788455409</v>
+        <v>-5.205879650430742</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6894</v>
+        <v>6877</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>374.3966105555962</v>
+        <v>376.6250367080219</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>357</v>
+        <v>119</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>47.4682294360459</v>
+        <v>34.08284963564368</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.46833537007456</v>
+        <v>19.17828688107932</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3170267844703854</v>
+        <v>2.548146622240816</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.483248708730279</v>
+        <v>-0.801403919206356</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6962</v>
+        <v>6887</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>370.0503328435211</v>
+        <v>376.5707570320053</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>37.4</v>
+        <v>36.05</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>49.8286373284399</v>
+        <v>51.95140835957848</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.53276730394539</v>
+        <v>6.687171541263587</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6414548582352081</v>
+        <v>0.7932768671587173</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0292241034137474</v>
+        <v>0.2452328788455409</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7717</v>
+        <v>6894</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>368.6094065145273</v>
+        <v>374.3966105555962</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>438</v>
+        <v>357</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>28.42853889134543</v>
+        <v>47.4682294360459</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>17.82194203018944</v>
+        <v>22.46833537007456</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5017567587764744</v>
+        <v>0.3170267844703854</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-12.04568160061233</v>
+        <v>-1.483248708730279</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7722</v>
+        <v>6962</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>365.498940800662</v>
+        <v>370.0503328435211</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>315.5</v>
+        <v>37.4</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.49303165234546</v>
+        <v>49.8286373284399</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>34.28805424694565</v>
+        <v>15.53276730394539</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2845745746616025</v>
+        <v>0.6414548582352081</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-1.333290386512374</v>
+        <v>0.0292241034137474</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7721</v>
+        <v>7717</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>364.7449309096094</v>
+        <v>368.6094065145273</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>438</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>40.1439477553674</v>
+        <v>28.42853889134543</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13.33731807556451</v>
+        <v>17.82194203018944</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3206377667418361</v>
+        <v>0.5017567587764744</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.046643385684303</v>
+        <v>-12.04568160061233</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7744</v>
+        <v>7722</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>361.8212777572104</v>
+        <v>365.498940800662</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>439.5</v>
+        <v>315.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>36.06769663931286</v>
+        <v>52.49303165234546</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14.2343659882918</v>
+        <v>34.28805424694565</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.1910502516327779</v>
+        <v>0.2845745746616025</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-3.444538108822419</v>
+        <v>-1.333290386512374</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7556</v>
+        <v>7721</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>361.1085388180397</v>
+        <v>364.7449309096094</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>273</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.27949317452638</v>
+        <v>40.1439477553674</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>11.70978036208509</v>
+        <v>13.33731807556451</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4393559589683018</v>
+        <v>0.3206377667418361</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.126109399463438</v>
+        <v>-1.046643385684303</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6937</v>
+        <v>7744</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>358.7226509564287</v>
+        <v>361.8212777572104</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>258</v>
+        <v>439.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>39.50093942846709</v>
+        <v>36.06769663931286</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>13.39352328321035</v>
+        <v>14.2343659882918</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.901015095291034</v>
+        <v>0.1910502516327779</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-1.931379363711285</v>
+        <v>-3.444538108822419</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7792</v>
+        <v>7556</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>356.0400261243658</v>
+        <v>361.1085388180397</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>40.9259497064976</v>
+        <v>48.27949317452638</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>18.27995068118158</v>
+        <v>11.70978036208509</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.3034617972279376</v>
+        <v>0.4393559589683018</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.7979414834686871</v>
+        <v>-1.126109399463438</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7734</v>
+        <v>6937</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>353.1357857208795</v>
+        <v>358.7226509564287</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2930</v>
+        <v>258</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>42.27394083510222</v>
+        <v>39.50093942846709</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.76870813136208</v>
+        <v>13.39352328321035</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3697378173885874</v>
+        <v>0.901015095291034</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-22.79341677331808</v>
+        <v>-1.931379363711285</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>7704</v>
+        <v>7792</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>349.9788709338052</v>
+        <v>356.0400261243658</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>62.4</v>
+        <v>255</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.58327714486511</v>
+        <v>40.9259497064976</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12.71517041492551</v>
+        <v>18.27995068118158</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5133505342444363</v>
+        <v>0.3034617972279376</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.3148763005556024</v>
+        <v>0.7979414834686871</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7805</v>
+        <v>7734</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>346.3508759490413</v>
+        <v>353.1357857208795</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>645</v>
+        <v>2930</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>27.86439455815668</v>
+        <v>42.27394083510222</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>27.35333878034668</v>
+        <v>19.76870813136208</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4895392046414939</v>
+        <v>0.3697378173885874</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-7.539043668094514</v>
+        <v>-22.79341677331808</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7821</v>
+        <v>7704</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>345.0012698133951</v>
+        <v>349.9788709338052</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>41.45</v>
+        <v>62.4</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>32.56261645644656</v>
+        <v>52.58327714486511</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.43538583361334</v>
+        <v>12.71517041492551</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.706820246363451</v>
+        <v>0.5133505342444363</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1235414360776954</v>
+        <v>0.3148763005556024</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7760</v>
+        <v>7805</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>344.5876240615587</v>
+        <v>346.3508759490413</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>32.9</v>
+        <v>645</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.68333848637384</v>
+        <v>27.86439455815668</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>40.73355781141049</v>
+        <v>27.35333878034668</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9720913842382296</v>
+        <v>0.4895392046414939</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.173120770360602</v>
+        <v>-7.539043668094514</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6967</v>
+        <v>7821</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>343.3877115469477</v>
+        <v>345.0012698133951</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>71.2</v>
+        <v>41.45</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.12037553959033</v>
+        <v>32.56261645644656</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9.097380629497737</v>
+        <v>20.43538583361334</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3767090159272119</v>
+        <v>0.706820246363451</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1152948965860996</v>
+        <v>-0.1235414360776954</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6855</v>
+        <v>7760</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>337.1335640519129</v>
+        <v>344.5876240615587</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>123.5</v>
+        <v>32.9</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.62132943028429</v>
+        <v>49.68333848637384</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.5649794224127</v>
+        <v>40.73355781141049</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.0413307680703284</v>
+        <v>0.9720913842382296</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1832735227449156</v>
+        <v>0.173120770360602</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6909</v>
+        <v>6967</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>334.6679747141383</v>
+        <v>343.3877115469477</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>55.5</v>
+        <v>71.2</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>55.5582395278435</v>
+        <v>49.12037553959033</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19.0373617324115</v>
+        <v>9.097380629497737</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8170393560783238</v>
+        <v>0.3767090159272119</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.208614245597999</v>
+        <v>0.1152948965860996</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6862</v>
+        <v>6855</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>334.3120284770715</v>
+        <v>337.1335640519129</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>183.5</v>
+        <v>123.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45.19419134337687</v>
+        <v>52.62132943028429</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>21.99510195127919</v>
+        <v>13.5649794224127</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.2642310512264157</v>
+        <v>0.0413307680703284</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-2.547636259395754</v>
+        <v>0.1832735227449156</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7753</v>
+        <v>6909</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>328.882788362502</v>
+        <v>334.6679747141383</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>42.15</v>
+        <v>55.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>47.75684184322395</v>
+        <v>55.5582395278435</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.41642949136636</v>
+        <v>19.0373617324115</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.3425605438001216</v>
+        <v>0.8170393560783238</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0456843379352931</v>
+        <v>1.208614245597999</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6994</v>
+        <v>6862</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>328.2210691433721</v>
+        <v>334.3120284770715</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>48.1</v>
+        <v>183.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>30.10513517739811</v>
+        <v>45.19419134337687</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>24.08755132009232</v>
+        <v>21.99510195127919</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5200454400403706</v>
+        <v>0.2642310512264157</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.8588339012126909</v>
+        <v>-2.547636259395754</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6971</v>
+        <v>7753</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>328.1436853371719</v>
+        <v>328.882788362502</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>27.95</v>
+        <v>42.15</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.58511217685987</v>
+        <v>47.75684184322395</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>22.21502309109113</v>
+        <v>20.41642949136636</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6443350103041258</v>
+        <v>0.3425605438001216</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1654161810643756</v>
+        <v>0.0456843379352931</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6919</v>
+        <v>6994</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>327.4803967396193</v>
+        <v>328.2210691433721</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>99</v>
+        <v>48.1</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.67819196873361</v>
+        <v>30.10513517739811</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>17.27154493109876</v>
+        <v>24.08755132009232</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4281904197195706</v>
+        <v>0.5200454400403706</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.4239410761052482</v>
+        <v>-0.8588339012126909</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8039</v>
+        <v>6971</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>322.6254509143867</v>
+        <v>328.1436853371719</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>137.5</v>
+        <v>27.95</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46.050538080976</v>
+        <v>54.58511217685987</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.5268503561313</v>
+        <v>22.21502309109113</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3523037050211356</v>
+        <v>0.6443350103041258</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.8329605815057312</v>
+        <v>0.1654161810643756</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7842</v>
+        <v>6919</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>320.3426070613905</v>
+        <v>327.4803967396193</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>34.5481270560599</v>
+        <v>48.67819196873361</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>25.58330624823728</v>
+        <v>17.27154493109876</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.2714201040546177</v>
+        <v>0.4281904197195706</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.484453800271579</v>
+        <v>0.4239410761052482</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7728</v>
+        <v>8039</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>319.1793915430285</v>
+        <v>322.6254509143867</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>656</v>
+        <v>137.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>37.93930719578227</v>
+        <v>46.050538080976</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.55120521949118</v>
+        <v>17.5268503561313</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5584660373974754</v>
+        <v>0.3523037050211356</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-6.112553281567966</v>
+        <v>-0.8329605815057312</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7738</v>
+        <v>7842</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>318.497022699745</v>
+        <v>320.3426070613905</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>166.5</v>
+        <v>98</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>41.39435482153322</v>
+        <v>34.5481270560599</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>22.37040624591616</v>
+        <v>25.58330624823728</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.353642910319551</v>
+        <v>0.2714201040546177</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1105749399504363</v>
+        <v>0.484453800271579</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6951</v>
+        <v>7728</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>313.7306116669932</v>
+        <v>319.1793915430285</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>76.59999999999999</v>
+        <v>656</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>32.76392253370983</v>
+        <v>37.93930719578227</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>26.84500216440628</v>
+        <v>10.55120521949118</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8741593667401175</v>
+        <v>0.5584660373974754</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.4011898578667867</v>
+        <v>-6.112553281567966</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7780</v>
+        <v>7738</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>303.985505271895</v>
+        <v>318.497022699745</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>18.05</v>
+        <v>166.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>42.90684612181823</v>
+        <v>41.39435482153322</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>16.42743790830811</v>
+        <v>22.37040624591616</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5114353632605447</v>
+        <v>0.353642910319551</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.0256969527859954</v>
+        <v>-0.1105749399504363</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6952</v>
+        <v>6951</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>303.8286802040519</v>
+        <v>313.7306116669932</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>35.9</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>43.39284281889423</v>
+        <v>32.76392253370983</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21.16480139951974</v>
+        <v>26.84500216440628</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5509051034418952</v>
+        <v>0.8741593667401175</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.034814603133991</v>
+        <v>-0.4011898578667867</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6913</v>
+        <v>7780</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>302.0733277166811</v>
+        <v>303.985505271895</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>118.5</v>
+        <v>18.05</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>37.97645718323741</v>
+        <v>42.90684612181823</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16.39371895836059</v>
+        <v>16.42743790830811</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.622276493883553</v>
+        <v>0.5114353632605447</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.16073198000937</v>
+        <v>-0.0256969527859954</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7765</v>
+        <v>6952</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>301.0476613761441</v>
+        <v>303.8286802040519</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>220.5</v>
+        <v>35.9</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>34.08612533795019</v>
+        <v>43.39284281889423</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>26.74673279251087</v>
+        <v>21.16480139951974</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2940241208282915</v>
+        <v>0.5509051034418952</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-3.720411825320449</v>
+        <v>0.034814603133991</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7786</v>
+        <v>6913</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>300.660440992951</v>
+        <v>302.0733277166811</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>123</v>
+        <v>118.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46.06009058403327</v>
+        <v>37.97645718323741</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>18.82032572535412</v>
+        <v>16.39371895836059</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.318600241676409</v>
+        <v>0.622276493883553</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.149312442854927</v>
+        <v>-1.16073198000937</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6921</v>
+        <v>7765</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>300.2188938213704</v>
+        <v>301.0476613761441</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>69</v>
+        <v>220.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>38.19939252680866</v>
+        <v>34.08612533795019</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.57789952424437</v>
+        <v>26.74673279251087</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.1794654633195266</v>
+        <v>0.2940241208282915</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.2188011485607455</v>
+        <v>-3.720411825320449</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7711</v>
+        <v>7786</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>296.5182545337976</v>
+        <v>300.660440992951</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>324</v>
+        <v>123</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>36.66055372531449</v>
+        <v>46.06009058403327</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.19847610888219</v>
+        <v>18.82032572535412</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3293312443350196</v>
+        <v>0.318600241676409</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-5.105517456893245</v>
+        <v>0.149312442854927</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7769</v>
+        <v>6921</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>296.2044924123263</v>
+        <v>300.2188938213704</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>6395</v>
+        <v>69</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>40.46484972236354</v>
+        <v>38.19939252680866</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.64819806656763</v>
+        <v>20.57789952424437</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8402185394503462</v>
+        <v>0.1794654633195266</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-141.0528949577997</v>
+        <v>0.2188011485607455</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7810</v>
+        <v>7711</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>286.5962456856524</v>
+        <v>296.5182545337976</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>197</v>
+        <v>324</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>37.79046842716673</v>
+        <v>36.66055372531449</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.65998803216468</v>
+        <v>18.19847610888219</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2298269496265867</v>
+        <v>0.3293312443350196</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.8988312354049599</v>
+        <v>-5.105517456893245</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6869</v>
+        <v>7769</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>286.1238457773999</v>
+        <v>296.2044924123263</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>74</v>
+        <v>6395</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>38.26863664742896</v>
+        <v>40.46484972236354</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21.3465697136272</v>
+        <v>18.64819806656763</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.8982137076121277</v>
+        <v>0.8402185394503462</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.6656472206663491</v>
+        <v>-141.0528949577997</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7747</v>
+        <v>7810</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>282.8333661322273</v>
+        <v>286.5962456856524</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>52.06447126147057</v>
+        <v>37.79046842716673</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5.251262422504854</v>
+        <v>14.65998803216468</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.0840135226958148</v>
+        <v>0.2298269496265867</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.3755243080091293</v>
+        <v>-0.8988312354049599</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6983</v>
+        <v>6869</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>282.6463465836558</v>
+        <v>286.1238457773999</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>350</v>
+        <v>74</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.54998499553024</v>
+        <v>38.26863664742896</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.64556953960032</v>
+        <v>21.3465697136272</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.2476160095127528</v>
+        <v>0.8982137076121277</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>2.34616232102028</v>
+        <v>-0.6656472206663491</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7740</v>
+        <v>7747</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>276.8686628703994</v>
+        <v>282.8333661322273</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>149.5</v>
+        <v>128</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.31846635145958</v>
+        <v>52.06447126147057</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>17.16148602895084</v>
+        <v>5.251262422504854</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.8795042914750414</v>
+        <v>0.0840135226958148</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.921240416523396</v>
+        <v>-0.3755243080091293</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7820</v>
+        <v>6983</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>276.2096128363443</v>
+        <v>282.6463465836558</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>111</v>
+        <v>350</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>30.28811044365547</v>
+        <v>43.54998499553024</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>28.41181197704183</v>
+        <v>11.64556953960032</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.2075334896986691</v>
+        <v>0.2476160095127528</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.5260701250881556</v>
+        <v>2.34616232102028</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7703</v>
+        <v>7740</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>270.2930139794025</v>
+        <v>276.8686628703994</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>199</v>
+        <v>149.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>44.60303992557217</v>
+        <v>39.31846635145958</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.02843287657701</v>
+        <v>17.16148602895084</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5434794330022427</v>
+        <v>0.8795042914750414</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.3737503933669939</v>
+        <v>-1.921240416523396</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6899</v>
+        <v>7820</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>266.3735539207213</v>
+        <v>276.2096128363443</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>57.6</v>
+        <v>111</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>40.38655867547781</v>
+        <v>30.28811044365547</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.54832776147384</v>
+        <v>28.41181197704183</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3165095507121993</v>
+        <v>0.2075334896986691</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.7448381769694334</v>
+        <v>0.5260701250881556</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8047</v>
+        <v>7703</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>265.3029489261285</v>
+        <v>270.2930139794025</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>48.4</v>
+        <v>199</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>49.067437907014</v>
+        <v>44.60303992557217</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>6.24900565982069</v>
+        <v>11.02843287657701</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.2201196554119095</v>
+        <v>0.5434794330022427</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1145006117906485</v>
+        <v>0.3737503933669939</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6918</v>
+        <v>6899</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>257.5012937350928</v>
+        <v>266.3735539207213</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>72.7</v>
+        <v>57.6</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.47206808714187</v>
+        <v>40.38655867547781</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>7.246823526321906</v>
+        <v>17.54832776147384</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.6564408524066015</v>
+        <v>0.3165095507121993</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0116871263151301</v>
+        <v>-0.7448381769694334</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8038</v>
+        <v>8047</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>256.8038978309789</v>
+        <v>265.3029489261285</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>38.6</v>
+        <v>48.4</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>37.83884305422743</v>
+        <v>49.067437907014</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>6.976543420255784</v>
+        <v>6.24900565982069</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.4667321166428712</v>
+        <v>0.2201196554119095</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1726464562304162</v>
+        <v>-0.1145006117906485</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6910</v>
+        <v>6918</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>255.3494633582847</v>
+        <v>257.5012937350928</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>27.2</v>
+        <v>72.7</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>37.98087867945146</v>
+        <v>43.47206808714187</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.52260594606272</v>
+        <v>7.246823526321906</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4403571947615741</v>
+        <v>0.6564408524066015</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.1246935733102045</v>
+        <v>-0.0116871263151301</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6854</v>
+        <v>8038</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>250.1536845215026</v>
+        <v>256.8038978309789</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>125</v>
+        <v>38.6</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>37.54508505686596</v>
+        <v>37.83884305422743</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>19.62821748775295</v>
+        <v>6.976543420255784</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5811239021636923</v>
+        <v>0.4667321166428712</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.479506377463176</v>
+        <v>-0.1726464562304162</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6969</v>
+        <v>6910</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>249.8800164221448</v>
+        <v>255.3494633582847</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>24.2</v>
+        <v>27.2</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>14.33896720196274</v>
+        <v>37.98087867945146</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>27.10783524814867</v>
+        <v>14.52260594606272</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.85751582611625</v>
+        <v>0.4403571947615741</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2084794154318947</v>
+        <v>-0.1246935733102045</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6863</v>
+        <v>6854</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>245.4659627989809</v>
+        <v>250.1536845215026</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>125</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>31.66499034567066</v>
+        <v>37.54508505686596</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>24.61923128256318</v>
+        <v>19.62821748775295</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.700910542029708</v>
+        <v>0.5811239021636923</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.8323151319793589</v>
+        <v>-0.479506377463176</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6965</v>
+        <v>6969</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>240.3494038333017</v>
+        <v>249.8800164221448</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>78.2</v>
+        <v>24.2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.12212354395006</v>
+        <v>14.33896720196274</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>23.07137282734163</v>
+        <v>27.10783524814867</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.1492677624524449</v>
+        <v>0.85751582611625</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.204107691267029</v>
+        <v>-0.2084794154318947</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5456,21 +5456,21 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7839</v>
+        <v>6924</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>233.8634059214663</v>
+        <v>248.0877783678848</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>46.85</v>
+        <v>125.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45.50986838284614</v>
+        <v>46.08560281542404</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>8.498821853901054</v>
+        <v>24.03537595486824</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2761780705718587</v>
+        <v>0.1099409620622657</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.080124180707942</v>
+        <v>-1.992565491703817</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7823</v>
+        <v>6863</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>233.3630758254</v>
+        <v>245.4659627989809</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>78.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>24.7801999571654</v>
+        <v>31.66499034567066</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>33.04739356250202</v>
+        <v>24.61923128256318</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.224674302459063</v>
+        <v>0.700910542029708</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.7330047984720283</v>
+        <v>-0.8323151319793589</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6997</v>
+        <v>6965</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>230.2098605235038</v>
+        <v>240.3494038333017</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.8726048129768</v>
+        <v>41.12212354395006</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>7.659331700212628</v>
+        <v>23.07137282734163</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.1270292929549554</v>
+        <v>0.1492677624524449</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.4071293333440153</v>
+        <v>-0.204107691267029</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7803</v>
+        <v>7839</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>224.3744320503067</v>
+        <v>233.8634059214663</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>23.3</v>
+        <v>46.85</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46.73272423456441</v>
+        <v>45.50986838284614</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.74128002033902</v>
+        <v>8.498821853901054</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.303488413592005</v>
+        <v>0.2761780705718587</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.224244853132284</v>
+        <v>-1.080124180707942</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7732</v>
+        <v>7823</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>213.0764859124387</v>
+        <v>233.3630758254</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>35.8</v>
+        <v>78.7</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.80796680530048</v>
+        <v>24.7801999571654</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>14.59575465646709</v>
+        <v>33.04739356250202</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.511525601856373</v>
+        <v>1.224674302459063</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1103490199376442</v>
+        <v>-0.7330047984720283</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6958</v>
+        <v>6997</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>212.2553056484929</v>
+        <v>230.2098605235038</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>16.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>37.31653536426776</v>
+        <v>50.8726048129768</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.08911941736286</v>
+        <v>7.659331700212628</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8946154436824788</v>
+        <v>0.1270292929549554</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0213616564079426</v>
+        <v>0.4071293333440153</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7730</v>
+        <v>7803</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>208.1013632709617</v>
+        <v>224.3744320503067</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>179</v>
+        <v>23.3</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.57788350867321</v>
+        <v>46.73272423456441</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>13.11300571481122</v>
+        <v>20.74128002033902</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3404475278533004</v>
+        <v>1.303488413592005</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.8834819357101575</v>
+        <v>0.224244853132284</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7705</v>
+        <v>7732</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>195.8849058037096</v>
+        <v>213.0764859124387</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>31.6</v>
+        <v>35.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>47.84360823407908</v>
+        <v>51.80796680530048</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.34295622107346</v>
+        <v>14.59575465646709</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.2498981700785976</v>
+        <v>0.511525601856373</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0576244171753258</v>
+        <v>-0.1103490199376442</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7818</v>
+        <v>6958</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>193.8666916679426</v>
+        <v>212.2553056484929</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>63</v>
+        <v>16.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>32.66121481639613</v>
+        <v>37.31653536426776</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>47.3516799509658</v>
+        <v>17.08911941736286</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6207049479813</v>
+        <v>0.8946154436824788</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>1.435450896955196</v>
+        <v>-0.0213616564079426</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8034</v>
+        <v>7730</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>190.498283844985</v>
+        <v>208.1013632709617</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>21.75</v>
+        <v>179</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>28.60999502195984</v>
+        <v>45.57788350867321</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>20.33316084029299</v>
+        <v>13.11300571481122</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6137354736246847</v>
+        <v>0.3404475278533004</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1247986122013071</v>
+        <v>-0.8834819357101575</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8011</v>
+        <v>7705</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>187.031624271462</v>
+        <v>195.8849058037096</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>17</v>
+        <v>31.6</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>33.81771129201815</v>
+        <v>47.84360823407908</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.04112779071932</v>
+        <v>18.34295622107346</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5910709008905926</v>
+        <v>0.2498981700785976</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0976280850996684</v>
+        <v>0.0576244171753258</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6865</v>
+        <v>7818</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>181.4353192583364</v>
+        <v>193.8666916679426</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>28.45</v>
+        <v>63</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>51.99831784761655</v>
+        <v>32.66121481639613</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.66570357178822</v>
+        <v>47.3516799509658</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.406906855318239</v>
+        <v>0.6207049479813</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.7166528535372354</v>
+        <v>1.435450896955196</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6934</v>
+        <v>8034</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>172.1091799840557</v>
+        <v>190.498283844985</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>66.5</v>
+        <v>21.75</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>36.63691709184182</v>
+        <v>28.60999502195984</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>24.36926875264032</v>
+        <v>20.33316084029299</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.7573356440033713</v>
+        <v>0.6137354736246847</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0416733784895075</v>
+        <v>-0.1247986122013071</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6895</v>
+        <v>8011</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>170.6273114112066</v>
+        <v>187.031624271462</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>142.5</v>
+        <v>17</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>35.51818353704357</v>
+        <v>33.81771129201815</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>17.97678166416915</v>
+        <v>18.04112779071932</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.607551755831014</v>
+        <v>0.5910709008905926</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-1.758641047021573</v>
+        <v>-0.0976280850996684</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6931</v>
+        <v>6865</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>166.2883925533916</v>
+        <v>181.4353192583364</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>39.9</v>
+        <v>28.45</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>36.48591974766124</v>
+        <v>51.99831784761655</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.24186743370182</v>
+        <v>16.66570357178822</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5323887466328679</v>
+        <v>1.406906855318239</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1187880678408368</v>
+        <v>0.7166528535372354</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6923</v>
+        <v>6934</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>164.6112548746023</v>
+        <v>172.1091799840557</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>38.1338726995185</v>
+        <v>36.63691709184182</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.72739039999019</v>
+        <v>24.36926875264032</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4711667910440146</v>
+        <v>0.7573356440033713</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.4149954561703621</v>
+        <v>-0.0416733784895075</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7736</v>
+        <v>6895</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>163.5694828794703</v>
+        <v>170.6273114112066</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>142.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>40.67546632135014</v>
+        <v>35.51818353704357</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.54018767583682</v>
+        <v>17.97678166416915</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.3246476142262116</v>
+        <v>1.607551755831014</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0247151947478613</v>
+        <v>-1.758641047021573</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7547</v>
+        <v>6931</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>163.4507525829861</v>
+        <v>166.2883925533916</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>56.4</v>
+        <v>39.9</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>36.11398159632782</v>
+        <v>36.48591974766124</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15.99232385125216</v>
+        <v>18.24186743370182</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.207093887506386</v>
+        <v>0.5323887466328679</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0320757619375409</v>
+        <v>0.1187880678408368</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6955</v>
+        <v>6923</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>163.3353339018219</v>
+        <v>164.6112548746023</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>16.91734849622063</v>
+        <v>38.1338726995185</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.77357417119869</v>
+        <v>13.72739039999019</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.0138192170031646</v>
+        <v>0.4711667910440146</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-9.217709982192174</v>
+        <v>-0.4149954561703621</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6936</v>
+        <v>7736</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>162.1023756130707</v>
+        <v>163.5694828794703</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>32.35</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>35.60141743214295</v>
+        <v>40.67546632135014</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.97888826004961</v>
+        <v>14.54018767583682</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.380030278229357</v>
+        <v>0.3246476142262116</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.1044727107049033</v>
+        <v>-0.0247151947478613</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>7772</v>
+        <v>7547</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>154.9824105959547</v>
+        <v>163.4507525829861</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>128</v>
+        <v>56.4</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>37.41060226814208</v>
+        <v>36.11398159632782</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.859485467808263</v>
+        <v>15.99232385125216</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.3524713438772495</v>
+        <v>0.207093887506386</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-1.080830530931038</v>
+        <v>0.0320757619375409</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6885</v>
+        <v>6955</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>149.7157284212669</v>
+        <v>163.3353339018219</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>39.3988705889108</v>
+        <v>16.91734849622063</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.34821239727869</v>
+        <v>11.77357417119869</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2167849544419302</v>
+        <v>0.0138192170031646</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2802279126085676</v>
+        <v>-9.217709982192174</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7770</v>
+        <v>6936</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>148.1108898099772</v>
+        <v>162.1023756130707</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>41.65</v>
+        <v>32.35</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.02962203340474</v>
+        <v>35.60141743214295</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>6.279498282493546</v>
+        <v>11.97888826004961</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6780446322879203</v>
+        <v>0.380030278229357</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0196194403973027</v>
+        <v>-0.1044727107049033</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6953</v>
+        <v>7772</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>145.7632625638936</v>
+        <v>154.9824105959547</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>225</v>
+        <v>128</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>40.77061185002151</v>
+        <v>37.41060226814208</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>18.40179638926507</v>
+        <v>8.859485467808263</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6024681059272241</v>
+        <v>0.3524713438772495</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0176606474951892</v>
+        <v>-1.080830530931038</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>8045</v>
+        <v>6885</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>140.95549056971</v>
+        <v>149.7157284212669</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>58.5</v>
+        <v>21.1</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>35.54652488375099</v>
+        <v>39.3988705889108</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12.23265556562503</v>
+        <v>17.34821239727869</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.3462817670479886</v>
+        <v>0.2167849544419302</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0837725298863176</v>
+        <v>-0.2802279126085676</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6925</v>
+        <v>7770</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>140.478368644894</v>
+        <v>148.1108898099772</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>58.9</v>
+        <v>41.65</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>40.0972872422466</v>
+        <v>46.02962203340474</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.97412237714918</v>
+        <v>6.279498282493546</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.10202483365665</v>
+        <v>0.6780446322879203</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.9062385236498104</v>
+        <v>0.0196194403973027</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6988</v>
+        <v>6953</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>139.9537263494072</v>
+        <v>145.7632625638936</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>13.3</v>
+        <v>225</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>27.39989132090626</v>
+        <v>40.77061185002151</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.90572432216823</v>
+        <v>18.40179638926507</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.3819189710518875</v>
+        <v>0.6024681059272241</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.07923685463122609</v>
+        <v>0.0176606474951892</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6873</v>
+        <v>8045</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>113.3286095718309</v>
+        <v>140.95549056971</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>82.7</v>
+        <v>58.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.81002207523749</v>
+        <v>35.54652488375099</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>12.69327991067535</v>
+        <v>12.23265556562503</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5104551203585934</v>
+        <v>0.3462817670479886</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0421342706461258</v>
+        <v>-0.0837725298863176</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6908</v>
+        <v>6925</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>95.0559192160256</v>
+        <v>140.478368644894</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>37.35</v>
+        <v>58.9</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>37.49922926518776</v>
+        <v>40.0972872422466</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>10.64027218897523</v>
+        <v>15.97412237714918</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.3718794088047099</v>
+        <v>0.10202483365665</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.1033626325924628</v>
+        <v>-0.9062385236498104</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,52 +6993,211 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
+        <v>6988</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>威力暘-創</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>139.9537263494072</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>27.39989132090626</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>14.90572432216823</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.3819189710518875</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>-0.07923685463122609</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>6873</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>泓德能源</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>113.3286095718309</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>46.81002207523749</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>12.69327991067535</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.5104551203585934</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-0.0421342706461258</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>6908</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>宏碁遊戲-創</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>95.0559192160256</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>37.35</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>37.49922926518776</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>10.64027218897523</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.3718794088047099</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.1033626325924628</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
         <v>7791</v>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>皇家可口</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D124" s="2" t="n">
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
         <v>50.55236191148355</v>
       </c>
-      <c r="E124" s="2" t="n">
+      <c r="E127" s="2" t="n">
         <v>62.4</v>
       </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H124" s="2" t="n">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
         <v>42.06556188250935</v>
       </c>
-      <c r="I124" s="2" t="n">
+      <c r="I127" s="2" t="n">
         <v>18.14181897288261</v>
       </c>
-      <c r="J124" s="2" t="n">
+      <c r="J127" s="2" t="n">
         <v>0.2986759349210851</v>
       </c>
-      <c r="K124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N124" s="2" t="n">
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
         <v>-0.1956899626627428</v>
       </c>
-      <c r="O124" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
